--- a/daily_matches/job_matches_2026-03-30.xlsx
+++ b/daily_matches/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a498e1d33bfb61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b853e0838aff05c5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-30.xlsx
+++ b/daily_matches/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
+          <t>Data Scientist, RAG, Redshift, CI/CD, Git, Snowflake, Redshift, PySpark, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Pinecone, S3, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a498e1d33bfb61</t>
+          <t>https://www.indeed.com/viewjob?jk=b912b59e0b8d6118</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>UPS Digital Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Keras, Git, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,112 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b853e0838aff05c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f10efa8aff5991b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UPS Digital Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Keras, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db79d5032b499540</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cargill</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wayzata, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=382bc7a4f3341bc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cargill</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fad1d4a13591a104</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-30.xlsx
+++ b/daily_matches/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, CI/CD, Git, Snowflake, Redshift, PySpark, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, Data Lake, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, S3, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b912b59e0b8d6118</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UPS Digital Senior Machine Learning Engineer</t>
+          <t>AI/Machine Learning Engineer - Python | TheLoops</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Copperleaf Technologies Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Keras, Git, R, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f10efa8aff5991b</t>
+          <t>https://www.indeed.com/viewjob?jk=0714a5bc619704bd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPS Digital Senior Machine Learning Engineer</t>
+          <t>AI Platform Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>JAVA Technical lead - Atlanta,GA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Keras, Git, R, Scala</t>
+          <t>Hugging Face, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,112 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db79d5032b499540</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa052a6fec50fdd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Senior Automation Controls Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382bc7a4f3341bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7bab52117e77ca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cbeaf171f6307db</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Platform Developer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Spry Methods, Inc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fad1d4a13591a104</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d1b3b1c37130ae0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-30.xlsx
+++ b/daily_matches/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GHX</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Redshift, Kinesis, Docker, Apache Airflow, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Azure ML, Azure ML Studio, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441872d9ed02e03f</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, Terraform, Git, Redshift</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2dcd3fa4ed5cbc2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=830e571e3cfdd5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=36e7b796ad09aceb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63198dd25f9047b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee89034bfa1ca14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, BigQuery, Data Lake, Apache Airflow, CI/CD, BigQuery, PySpark, Kafka</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=623c77a91442bd42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Google Gemini AI Architect</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, BigQuery, Kubernetes, Terraform</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c83cb26fd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=c81617b7963aadb4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Athena, Synapse, Data Lake, GitHub Actions, Git, PySpark, Power BI, Python</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=28a98621614d8098</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Athena, Synapse, Data Lake, GitHub Actions, Git, PySpark, Power BI, Python</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30041f511b9859</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, XGBoost, AWS SageMaker, CI/CD, Jenkins, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60cd311a13167333</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53223ee8f8f61f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a794a4fad5ad9bde</t>
+          <t>https://www.indeed.com/viewjob?jk=89b3ec48658b5cdb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer - CDE</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, EC2, Glue, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
+          <t>https://www.indeed.com/viewjob?jk=1c5521cd8930ff37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer 2 (Full Stack - AI, SQL, React, Python)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Elgin, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0372821634552b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=3fabd5ca82ceb84e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack</t>
+          <t>Software Engineer, Agentic Development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PathAI</t>
+          <t>Altisource</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Docker, Git, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c0a5776037404b</t>
+          <t>https://www.indeed.com/viewjob?jk=baa9fdf1cf622d95</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Git, Snowflake, Databricks, Kafka, Hadoop, Cassandra, NoSQL, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, EC2, Docker, CI/CD, Databricks, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=18c56c9fa1c0e5c9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI/ML</t>
+          <t>Senior AI Platform Engineer - Technology R&amp;D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Signant Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6a1189a35cd04a</t>
+          <t>https://www.indeed.com/viewjob?jk=a63e110419ffd00e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HYPERPROOF</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6aee1b0f55f34d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e986546cd488fc2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mobile Software Engineer, iOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>StockX</t>
+          <t>Brivo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Databricks, Kafka, Hadoop, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, Copilot, CI/CD, Jenkins, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a52d3ff88f626ae</t>
+          <t>https://www.indeed.com/viewjob?jk=96d7d9f54bae453c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer AI and Machine Learning</t>
+          <t>Mobile Software Engineer, iOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brivo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, Copilot, CI/CD, Jenkins, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd6064c4bc6e448</t>
+          <t>https://www.indeed.com/viewjob?jk=283de2f462b051a3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Think Big Technology</t>
+          <t>Sapphire Media LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belleville, NJ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Hugging Face, FastAPI, Docker, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2b146ea6b7e2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bff5467a6943a96d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Biomedical Informatics</t>
+          <t>CCB Risk Modeling - AI ML Senior Associate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, TensorFlow, XGBoost, Git, Hadoop, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c56905347348ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fbfda13c12522472</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Engagement Strategist, Marketing Applied Sciences</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>CI/CD, Jenkins, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d73e1529aa13ea</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering Generative AI - Officer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,567 +1231,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d9adae18656bb</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI Infrastructure &amp; Platform Ops Engineer (junior career)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Synapse Health</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Skokie, IL, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f3b7447c12b208</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Autonomy Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>University of Dayton</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=804a5f1c2785ec7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Allen Control Systems</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=727a28daad1c98d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BAE Systems USA</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Fort Walton Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, AWS SageMaker, Glue, Data Lake, Docker, Kubernetes, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a692f38cfafc01b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Feathr</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Gainesville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, EC2, Docker, Kubernetes, AKS, CI/CD, Git, MongoDB, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=462b8d3c3066abf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer - AI/ML</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c64b37ca863fffbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Afresh</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe6f3b46601eb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Jr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Infillion</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2283c97cf1ee62fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Software Data Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Ensemble Health Partners</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Terraform, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be88399cc5b70a3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BetMGM LLC</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Snowflake, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3924dcb59d2fca2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Solutions Architect – Cloud Platforms</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>First Quality</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Terraform, Git, Databricks, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Scientist, AI/ML – Visa Consulting and Analytics</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae301628ee74378</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist III</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, XGBoost, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2cdd3e96630f6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist III</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>LexisNexis Risk Solutions</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, XGBoost, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02fbf14e76638127</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, Analytics</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Discord</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7751f21924b6ccfe</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Engineer – Performance &amp; Insights</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Bloom</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Git, Redshift, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0083ec800cffbbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f5251f10509cee</t>
         </is>
       </c>
     </row>
